--- a/data/trans_bre/IP1011-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1011-Habitat-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,41</t>
+          <t>-0,79; 1,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,77</t>
+          <t>-0,87; 1,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,03</t>
+          <t>-0,63; 1,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,0</t>
+          <t>-1,69; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 0,0</t>
+          <t>-1,74; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,29</t>
+          <t>-0,55; 0,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,41</t>
+          <t>-0,34; 0,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,0</t>
+          <t>-0,45; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">

--- a/data/trans_bre/IP1011-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1011-Habitat-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,37</t>
+          <t>-0,79; 1,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,77</t>
+          <t>-0,85; 1,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,02</t>
+          <t>-0,63; 1,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,0</t>
+          <t>-1,53; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,0</t>
+          <t>-1,62; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,28</t>
+          <t>-0,47; 0,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,43</t>
+          <t>-0,35; 0,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,0</t>
+          <t>-0,54; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">

--- a/data/trans_bre/IP1011-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1011-Habitat-trans_bre.xlsx
@@ -634,12 +634,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,35</t>
+          <t>-0,79; 1,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,69</t>
+          <t>-0,86; 1,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,35</t>
+          <t>-0,92; 1,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,24</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,0</t>
+          <t>-1,92; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,0</t>
+          <t>-1,65; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,0</t>
+          <t>-2,43; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,37</t>
+          <t>-0,54; 0,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,0</t>
+          <t>-0,48; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">

--- a/data/trans_bre/IP1011-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP1011-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,121 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,04</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,13</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,88%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>30,3%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.04279166365106996</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.1288902223976443</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.1087591592754286</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.3029994143524615</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-0,79; 1,41</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-0,86; 1,77</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-0.7897159593616948</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-0.8586882015170846</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.411744230384089</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.773808107834043</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,69%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-0,92; 1,03</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.0242004989233676</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.07694401742726312</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,42</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-0.9211006146211428</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,14</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.030066576224815</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,157 +725,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,32</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,35</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.4237748448760135</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,92; 0,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,65; 0,0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,43; 0,0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="n">
+        <v>2.142103874754812</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.3370136669552471</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.3243064280039792</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.3465752210408519</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.923004359883034</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.648893917759308</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.430748704136168</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-31,79%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>12,98%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,54; 0,29</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-0,35; 0,41</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,48; 0,0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.08664363801493465</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.02294242940948221</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.09572876968546686</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-0.3178686722328453</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1297535345669683</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.5411580299797969</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.3515001540333187</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.4777323077832794</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.2890545264637948</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.4142577164605172</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -993,13 +924,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
